--- a/Excel/MapData.xlsx
+++ b/Excel/MapData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="32">
   <si>
     <t>int</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>石头</t>
+  </si>
+  <si>
+    <t>人</t>
   </si>
   <si>
     <t>狼</t>
@@ -2452,7 +2455,7 @@
         <v>10054</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C72" s="1">
         <v>0</v>
@@ -2464,7 +2467,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="1">
-        <v>20001</v>
+        <v>20007</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:6">
@@ -2592,7 +2595,7 @@
         <v>10061</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C79" s="1">
         <v>0</v>
@@ -2852,7 +2855,7 @@
         <v>10074</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C92" s="1">
         <v>0</v>

--- a/Excel/MapData.xlsx
+++ b/Excel/MapData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="33">
   <si>
     <t>int</t>
   </si>
@@ -56,6 +56,9 @@
     <t>对应MaskData中面具的ID</t>
   </si>
   <si>
+    <t>对应的关卡</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -72,6 +75,9 @@
   </si>
   <si>
     <t>maskID</t>
+  </si>
+  <si>
+    <t>LevelID</t>
   </si>
   <si>
     <t>E_Volume</t>
@@ -98,31 +104,28 @@
     <t>2x1</t>
   </si>
   <si>
-    <t>老鼠</t>
+    <t>Mouse</t>
   </si>
   <si>
-    <t>巧克力</t>
+    <t>Chocolate</t>
   </si>
   <si>
-    <t>栅栏</t>
+    <t>Fence</t>
   </si>
   <si>
-    <t>磁带</t>
+    <t>Cassette</t>
   </si>
   <si>
-    <t>路灯</t>
+    <t>Streetlight</t>
   </si>
   <si>
-    <t>乌鸦</t>
+    <t>Crow</t>
   </si>
   <si>
-    <t>石头</t>
+    <t>Rock</t>
   </si>
   <si>
-    <t>人</t>
-  </si>
-  <si>
-    <t>狼</t>
+    <t>Wolf</t>
   </si>
 </sst>
 </file>
@@ -135,13 +138,34 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF666666"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -288,12 +312,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -304,12 +340,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,12 +512,42 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -608,141 +668,159 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1270,25 +1348,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F96"/>
-  <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:O111"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="4" width="17.3055555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.9907407407407" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.212962962963" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17.3083333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.9916666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.2166666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.6666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.4444444444444" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13.6111111111111" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.8518518518519" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.1111111111111" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.2222222222222" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5555555555556" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.23148148148148" style="1"/>
+    <col min="8" max="8" width="24.4416666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.775" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6083333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.85" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6083333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.225" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5583333333333" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1307,8 +1385,11 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="101" customHeight="1" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="101" customHeight="1" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1327,30 +1408,36 @@
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -1362,1592 +1449,2817 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="14.25" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:12">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" ht="14.25" spans="1:12">
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" ht="14.25" spans="1:12">
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="10" ht="14.25" spans="1:12">
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" ht="14.25" spans="1:12">
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" ht="14.25" spans="1:12">
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" ht="14.25" spans="1:12">
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:12">
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:12">
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:12">
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="17" ht="14.25" spans="1:15">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" ht="14.25" spans="1:15">
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A19" s="1">
         <v>10001</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>23</v>
+      <c r="B19" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
       </c>
-      <c r="D19" s="1">
-        <v>5</v>
-      </c>
-      <c r="E19" s="1">
-        <v>5</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="D19" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4">
         <v>10001</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:6">
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A20" s="1">
         <v>10002</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>24</v>
+      <c r="B20" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
       </c>
-      <c r="D20" s="1">
-        <v>9</v>
-      </c>
-      <c r="E20" s="1">
-        <v>5</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="D20" s="4">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4">
         <v>20002</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:6">
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A21" s="1">
         <v>10003</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>23</v>
+      <c r="B21" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
       </c>
-      <c r="D21" s="1">
-        <v>11</v>
-      </c>
-      <c r="E21" s="1">
-        <v>3</v>
-      </c>
-      <c r="F21" s="1">
+      <c r="D21" s="4">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F21" s="4">
         <v>10001</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:6">
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A22" s="1">
         <v>10004</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>23</v>
+      <c r="B22" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
       </c>
-      <c r="D22" s="1">
-        <v>11</v>
-      </c>
-      <c r="E22" s="1">
-        <v>9</v>
-      </c>
-      <c r="F22" s="1">
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4">
+        <v>4</v>
+      </c>
+      <c r="F22" s="4">
         <v>10001</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:6">
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A23" s="1">
         <v>10005</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>23</v>
+      <c r="B23" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C23" s="1">
         <v>0</v>
       </c>
-      <c r="D23" s="1">
-        <v>12</v>
-      </c>
-      <c r="E23" s="1">
-        <v>6</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="D23" s="4">
+        <v>3</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
         <v>10001</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:6">
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A24" s="1">
         <v>10006</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>25</v>
+      <c r="B24" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
       </c>
-      <c r="D24" s="1">
-        <v>14</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="D24" s="4">
+        <v>7</v>
+      </c>
+      <c r="E24" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F24" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:6">
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A25" s="1">
         <v>10007</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>25</v>
+      <c r="B25" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C25" s="1">
         <v>0</v>
       </c>
-      <c r="D25" s="1">
-        <v>14</v>
-      </c>
-      <c r="E25" s="1">
-        <v>2</v>
-      </c>
-      <c r="F25" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:6">
+      <c r="D25" s="4">
+        <v>7</v>
+      </c>
+      <c r="E25" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F25" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A26" s="1">
         <v>10008</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>25</v>
+      <c r="B26" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
       </c>
-      <c r="D26" s="1">
-        <v>14</v>
-      </c>
-      <c r="E26" s="1">
-        <v>3</v>
-      </c>
-      <c r="F26" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:6">
+      <c r="D26" s="4">
+        <v>7</v>
+      </c>
+      <c r="E26" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F26" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A27" s="1">
         <v>10009</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>25</v>
+      <c r="B27" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C27" s="1">
         <v>0</v>
       </c>
-      <c r="D27" s="1">
-        <v>14</v>
-      </c>
-      <c r="E27" s="1">
-        <v>4</v>
-      </c>
-      <c r="F27" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:6">
+      <c r="D27" s="4">
+        <v>7</v>
+      </c>
+      <c r="E27" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F27" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A28" s="1">
         <v>10010</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>25</v>
+      <c r="B28" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C28" s="1">
         <v>0</v>
       </c>
-      <c r="D28" s="1">
-        <v>14</v>
-      </c>
-      <c r="E28" s="1">
-        <v>5</v>
-      </c>
-      <c r="F28" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="D28" s="4">
+        <v>7</v>
+      </c>
+      <c r="E28" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F28" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A29" s="1">
         <v>10011</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>25</v>
+      <c r="B29" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C29" s="1">
         <v>0</v>
       </c>
-      <c r="D29" s="1">
-        <v>14</v>
-      </c>
-      <c r="E29" s="1">
-        <v>6</v>
-      </c>
-      <c r="F29" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:6">
+      <c r="D29" s="4">
+        <v>7</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A30" s="1">
         <v>10012</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>25</v>
+      <c r="B30" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C30" s="1">
         <v>0</v>
       </c>
-      <c r="D30" s="1">
-        <v>14</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="D30" s="4">
         <v>7</v>
       </c>
-      <c r="F30" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:6">
+      <c r="E30" s="4">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A31" s="1">
         <v>10013</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>25</v>
+      <c r="B31" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C31" s="1">
         <v>0</v>
       </c>
-      <c r="D31" s="1">
-        <v>14</v>
-      </c>
-      <c r="E31" s="1">
-        <v>8</v>
-      </c>
-      <c r="F31" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:6">
+      <c r="D31" s="4">
+        <v>7</v>
+      </c>
+      <c r="E31" s="4">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A32" s="1">
         <v>10014</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>25</v>
+      <c r="B32" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C32" s="1">
         <v>0</v>
       </c>
-      <c r="D32" s="1">
-        <v>14</v>
-      </c>
-      <c r="E32" s="1">
-        <v>9</v>
-      </c>
-      <c r="F32" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:6">
+      <c r="D32" s="4">
+        <v>7</v>
+      </c>
+      <c r="E32" s="4">
+        <v>3</v>
+      </c>
+      <c r="F32" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A33" s="1">
         <v>10015</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>25</v>
+      <c r="B33" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C33" s="1">
         <v>0</v>
       </c>
-      <c r="D33" s="1">
-        <v>14</v>
-      </c>
-      <c r="E33" s="1">
-        <v>10</v>
-      </c>
-      <c r="F33" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:6">
+      <c r="D33" s="4">
+        <v>7</v>
+      </c>
+      <c r="E33" s="4">
+        <v>4</v>
+      </c>
+      <c r="F33" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A34" s="1">
         <v>10016</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>26</v>
+      <c r="B34" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C34" s="1">
         <v>0</v>
       </c>
-      <c r="D34" s="1">
-        <v>15</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D34" s="4">
+        <v>7</v>
+      </c>
+      <c r="E34" s="4">
         <v>5</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+    </row>
+    <row r="35" s="2" customFormat="1" ht="14.25" spans="1:15">
+      <c r="A35" s="2">
+        <v>10017</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4">
+        <v>8</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4">
         <v>20001</v>
       </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:6">
-      <c r="A35" s="1">
-        <v>10017</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0</v>
-      </c>
-      <c r="D35" s="1">
-        <v>17</v>
-      </c>
-      <c r="E35" s="1">
-        <v>4</v>
-      </c>
-      <c r="F35" s="1">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:6">
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A36" s="1">
         <v>10018</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>27</v>
+      <c r="B36" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C36" s="1">
         <v>2</v>
       </c>
-      <c r="D36" s="1">
-        <v>17</v>
-      </c>
-      <c r="E36" s="1">
-        <v>5</v>
-      </c>
-      <c r="F36" s="1">
-        <v>20004</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:6">
+      <c r="D36" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E36" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F36" s="4">
+        <v>10001</v>
+      </c>
+      <c r="G36" s="2">
+        <v>2</v>
+      </c>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A37" s="1">
         <v>10019</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>23</v>
+      <c r="B37" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C37" s="1">
         <v>0</v>
       </c>
-      <c r="D37" s="1">
-        <v>17</v>
-      </c>
-      <c r="E37" s="1">
-        <v>7</v>
-      </c>
-      <c r="F37" s="1">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:6">
+      <c r="D37" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E37" s="4">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4">
+        <v>20004</v>
+      </c>
+      <c r="G37" s="2">
+        <v>2</v>
+      </c>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A38" s="1">
         <v>10020</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>23</v>
+      <c r="B38" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C38" s="1">
         <v>0</v>
       </c>
-      <c r="D38" s="1">
-        <v>18</v>
-      </c>
-      <c r="E38" s="1">
-        <v>5</v>
-      </c>
-      <c r="F38" s="1">
+      <c r="D38" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E38" s="4">
+        <v>2</v>
+      </c>
+      <c r="F38" s="4">
         <v>10001</v>
       </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:6">
+      <c r="G38" s="2">
+        <v>2</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A39" s="1">
         <v>10021</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>27</v>
+      <c r="B39" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C39" s="1">
         <v>2</v>
       </c>
-      <c r="D39" s="1">
-        <v>24</v>
-      </c>
-      <c r="E39" s="1">
-        <v>5</v>
-      </c>
-      <c r="F39" s="1">
-        <v>20004</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:6">
+      <c r="D39" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4">
+        <v>10001</v>
+      </c>
+      <c r="G39" s="2">
+        <v>2</v>
+      </c>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A40" s="1">
         <v>10022</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>28</v>
+      <c r="B40" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C40" s="1">
         <v>0</v>
       </c>
-      <c r="D40" s="1">
-        <v>27</v>
-      </c>
-      <c r="E40" s="1">
-        <v>5</v>
-      </c>
-      <c r="F40" s="1">
-        <v>10003</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:6">
+      <c r="D40" s="4">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4">
+        <v>20004</v>
+      </c>
+      <c r="G40" s="2">
+        <v>2</v>
+      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A41" s="1">
         <v>10023</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>25</v>
+      <c r="B41" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="C41" s="1">
         <v>0</v>
       </c>
-      <c r="D41" s="1">
-        <v>31</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:6">
+      <c r="D41" s="4">
+        <v>6</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4">
+        <v>10003</v>
+      </c>
+      <c r="G41" s="2">
+        <v>2</v>
+      </c>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A42" s="1">
         <v>10024</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>25</v>
+      <c r="B42" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C42" s="1">
         <v>0</v>
       </c>
-      <c r="D42" s="1">
-        <v>31</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D42" s="4">
+        <v>9</v>
+      </c>
+      <c r="E42" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F42" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G42" s="2">
         <v>2</v>
       </c>
-      <c r="F42" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:6">
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A43" s="1">
         <v>10025</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>25</v>
+      <c r="B43" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C43" s="1">
         <v>0</v>
       </c>
-      <c r="D43" s="1">
-        <v>31</v>
-      </c>
-      <c r="E43" s="1">
-        <v>3</v>
-      </c>
-      <c r="F43" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="1:6">
+      <c r="D43" s="4">
+        <v>9</v>
+      </c>
+      <c r="E43" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F43" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G43" s="2">
+        <v>2</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A44" s="1">
         <v>10026</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>25</v>
+      <c r="B44" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C44" s="1">
         <v>0</v>
       </c>
-      <c r="D44" s="1">
-        <v>31</v>
-      </c>
-      <c r="E44" s="1">
-        <v>4</v>
-      </c>
-      <c r="F44" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="1:6">
+      <c r="D44" s="4">
+        <v>9</v>
+      </c>
+      <c r="E44" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F44" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G44" s="2">
+        <v>2</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A45" s="1">
         <v>10027</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>25</v>
+      <c r="B45" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C45" s="1">
         <v>0</v>
       </c>
-      <c r="D45" s="1">
-        <v>31</v>
-      </c>
-      <c r="E45" s="1">
-        <v>5</v>
-      </c>
-      <c r="F45" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" spans="1:6">
+      <c r="D45" s="4">
+        <v>9</v>
+      </c>
+      <c r="E45" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F45" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G45" s="2">
+        <v>2</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A46" s="1">
         <v>10028</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>25</v>
+      <c r="B46" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C46" s="1">
         <v>0</v>
       </c>
-      <c r="D46" s="1">
-        <v>31</v>
-      </c>
-      <c r="E46" s="1">
-        <v>6</v>
-      </c>
-      <c r="F46" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" spans="1:6">
+      <c r="D46" s="4">
+        <v>9</v>
+      </c>
+      <c r="E46" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F46" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G46" s="2">
+        <v>2</v>
+      </c>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A47" s="1">
         <v>10029</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>25</v>
+      <c r="B47" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C47" s="1">
         <v>0</v>
       </c>
-      <c r="D47" s="1">
-        <v>31</v>
-      </c>
-      <c r="E47" s="1">
-        <v>7</v>
-      </c>
-      <c r="F47" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" spans="1:6">
+      <c r="D47" s="4">
+        <v>9</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G47" s="2">
+        <v>2</v>
+      </c>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A48" s="1">
         <v>10030</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>25</v>
+      <c r="B48" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C48" s="1">
         <v>0</v>
       </c>
-      <c r="D48" s="1">
-        <v>31</v>
-      </c>
-      <c r="E48" s="1">
-        <v>8</v>
-      </c>
-      <c r="F48" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" spans="1:6">
+      <c r="D48" s="4">
+        <v>9</v>
+      </c>
+      <c r="E48" s="4">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G48" s="2">
+        <v>2</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A49" s="1">
         <v>10031</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>25</v>
+      <c r="B49" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C49" s="1">
         <v>0</v>
       </c>
-      <c r="D49" s="1">
-        <v>31</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="D49" s="4">
         <v>9</v>
       </c>
-      <c r="F49" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" spans="1:6">
+      <c r="E49" s="4">
+        <v>2</v>
+      </c>
+      <c r="F49" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G49" s="2">
+        <v>2</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A50" s="1">
         <v>10032</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>25</v>
+      <c r="B50" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C50" s="1">
         <v>0</v>
       </c>
-      <c r="D50" s="1">
-        <v>31</v>
-      </c>
-      <c r="E50" s="1">
-        <v>10</v>
-      </c>
-      <c r="F50" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="1:6">
+      <c r="D50" s="4">
+        <v>9</v>
+      </c>
+      <c r="E50" s="4">
+        <v>3</v>
+      </c>
+      <c r="F50" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G50" s="2">
+        <v>2</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A51" s="1">
         <v>10033</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>26</v>
+      <c r="B51" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C51" s="1">
         <v>0</v>
       </c>
-      <c r="D51" s="1">
-        <v>32</v>
-      </c>
-      <c r="E51" s="1">
-        <v>5</v>
-      </c>
-      <c r="F51" s="1">
-        <v>20001</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="1:6">
+      <c r="D51" s="4">
+        <v>9</v>
+      </c>
+      <c r="E51" s="4">
+        <v>4</v>
+      </c>
+      <c r="F51" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G51" s="2">
+        <v>2</v>
+      </c>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A52" s="1">
         <v>10034</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>23</v>
+      <c r="B52" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C52" s="1">
         <v>0</v>
       </c>
-      <c r="D52" s="1">
-        <v>34</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="D52" s="4">
+        <v>9</v>
+      </c>
+      <c r="E52" s="4">
         <v>5</v>
       </c>
-      <c r="F52" s="1">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:6">
-      <c r="A53" s="1">
+      <c r="F52" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G52" s="2">
+        <v>2</v>
+      </c>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+    </row>
+    <row r="53" s="2" customFormat="1" ht="14.25" spans="1:15">
+      <c r="A53" s="2">
         <v>10035</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" s="1">
-        <v>0</v>
-      </c>
-      <c r="D53" s="1">
-        <v>37</v>
-      </c>
-      <c r="E53" s="1">
-        <v>5</v>
-      </c>
-      <c r="F53" s="1">
-        <v>20003</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="1:6">
+      <c r="B53" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="2">
+        <v>0</v>
+      </c>
+      <c r="D53" s="4">
+        <v>10</v>
+      </c>
+      <c r="E53" s="4">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4">
+        <v>20001</v>
+      </c>
+      <c r="G53" s="2">
+        <v>2</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A54" s="1">
         <v>10036</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>24</v>
+      <c r="B54" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C54" s="1">
         <v>0</v>
       </c>
-      <c r="D54" s="1">
-        <v>38</v>
-      </c>
-      <c r="E54" s="1">
-        <v>2</v>
-      </c>
-      <c r="F54" s="1">
-        <v>20002</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="1:6">
+      <c r="D54" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E54" s="4">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4">
+        <v>10001</v>
+      </c>
+      <c r="G54" s="2">
+        <v>3</v>
+      </c>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="6"/>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A55" s="1">
         <v>10037</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>29</v>
+      <c r="B55" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C55" s="1">
         <v>0</v>
       </c>
-      <c r="D55" s="1">
-        <v>38</v>
-      </c>
-      <c r="E55" s="1">
-        <v>5</v>
-      </c>
-      <c r="F55" s="1">
+      <c r="D55" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E55" s="4">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4">
         <v>20003</v>
       </c>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="1:6">
+      <c r="G55" s="2">
+        <v>3</v>
+      </c>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A56" s="1">
         <v>10038</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>27</v>
+      <c r="B56" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C56" s="1">
         <v>2</v>
       </c>
-      <c r="D56" s="1">
-        <v>38</v>
-      </c>
-      <c r="E56" s="1">
-        <v>8</v>
-      </c>
-      <c r="F56" s="1">
-        <v>20004</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="1:6">
+      <c r="D56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E56" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F56" s="4">
+        <v>20002</v>
+      </c>
+      <c r="G56" s="2">
+        <v>3</v>
+      </c>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A57" s="1">
         <v>10039</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>29</v>
+      <c r="B57" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C57" s="1">
         <v>0</v>
       </c>
-      <c r="D57" s="1">
-        <v>39</v>
-      </c>
-      <c r="E57" s="1">
-        <v>5</v>
-      </c>
-      <c r="F57" s="1">
+      <c r="D57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E57" s="4">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4">
         <v>20003</v>
       </c>
-    </row>
-    <row r="58" s="1" customFormat="1" spans="1:6">
+      <c r="G57" s="2">
+        <v>3</v>
+      </c>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A58" s="1">
         <v>10040</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>23</v>
+      <c r="B58" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C58" s="1">
         <v>0</v>
       </c>
-      <c r="D58" s="1">
-        <v>39</v>
-      </c>
-      <c r="E58" s="1">
-        <v>8</v>
-      </c>
-      <c r="F58" s="1">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" spans="1:6">
+      <c r="D58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E58" s="4">
+        <v>3</v>
+      </c>
+      <c r="F58" s="4">
+        <v>20004</v>
+      </c>
+      <c r="G58" s="2">
+        <v>3</v>
+      </c>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A59" s="1">
         <v>10041</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>23</v>
+      <c r="B59" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C59" s="1">
         <v>0</v>
       </c>
-      <c r="D59" s="1">
-        <v>41</v>
-      </c>
-      <c r="E59" s="1">
-        <v>2</v>
-      </c>
-      <c r="F59" s="1">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" spans="1:6">
+      <c r="D59" s="4">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4">
+        <v>20003</v>
+      </c>
+      <c r="G59" s="2">
+        <v>3</v>
+      </c>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A60" s="1">
         <v>10042</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>27</v>
+      <c r="B60" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C60" s="1">
         <v>2</v>
       </c>
-      <c r="D60" s="1">
-        <v>43</v>
-      </c>
-      <c r="E60" s="1">
-        <v>5</v>
-      </c>
-      <c r="F60" s="1">
-        <v>20004</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" spans="1:6">
+      <c r="D60" s="4">
+        <v>0</v>
+      </c>
+      <c r="E60" s="4">
+        <v>3</v>
+      </c>
+      <c r="F60" s="4">
+        <v>10001</v>
+      </c>
+      <c r="G60" s="2">
+        <v>3</v>
+      </c>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A61" s="1">
         <v>10043</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>28</v>
+      <c r="B61" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C61" s="1">
         <v>0</v>
       </c>
-      <c r="D61" s="1">
-        <v>46</v>
-      </c>
-      <c r="E61" s="1">
-        <v>5</v>
-      </c>
-      <c r="F61" s="1">
-        <v>10003</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" spans="1:6">
+      <c r="D61" s="4">
+        <v>3</v>
+      </c>
+      <c r="E61" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F61" s="4">
+        <v>10001</v>
+      </c>
+      <c r="G61" s="2">
+        <v>3</v>
+      </c>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A62" s="1">
         <v>10044</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>25</v>
+      <c r="B62" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="C62" s="1">
         <v>0</v>
       </c>
-      <c r="D62" s="1">
-        <v>50</v>
-      </c>
-      <c r="E62" s="1">
-        <v>1</v>
-      </c>
-      <c r="F62" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" spans="1:6">
+      <c r="D62" s="4">
+        <v>5</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4">
+        <v>20004</v>
+      </c>
+      <c r="G62" s="2">
+        <v>3</v>
+      </c>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A63" s="1">
         <v>10045</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>25</v>
+      <c r="B63" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="C63" s="1">
         <v>0</v>
       </c>
-      <c r="D63" s="1">
-        <v>50</v>
-      </c>
-      <c r="E63" s="1">
-        <v>2</v>
-      </c>
-      <c r="F63" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="1:6">
+      <c r="D63" s="4">
+        <v>8</v>
+      </c>
+      <c r="E63" s="4">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4">
+        <v>10003</v>
+      </c>
+      <c r="G63" s="2">
+        <v>3</v>
+      </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A64" s="1">
         <v>10046</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>25</v>
+      <c r="B64" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C64" s="1">
         <v>0</v>
       </c>
-      <c r="D64" s="1">
-        <v>50</v>
-      </c>
-      <c r="E64" s="1">
+      <c r="D64" s="4">
+        <v>10</v>
+      </c>
+      <c r="E64" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F64" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G64" s="2">
         <v>3</v>
       </c>
-      <c r="F64" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:6">
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A65" s="1">
         <v>10047</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>25</v>
+      <c r="B65" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C65" s="1">
         <v>0</v>
       </c>
-      <c r="D65" s="1">
-        <v>50</v>
-      </c>
-      <c r="E65" s="1">
-        <v>4</v>
-      </c>
-      <c r="F65" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" spans="1:6">
+      <c r="D65" s="4">
+        <v>10</v>
+      </c>
+      <c r="E65" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F65" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G65" s="2">
+        <v>3</v>
+      </c>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A66" s="1">
         <v>10048</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>25</v>
+      <c r="B66" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C66" s="1">
         <v>0</v>
       </c>
-      <c r="D66" s="1">
-        <v>50</v>
-      </c>
-      <c r="E66" s="1">
-        <v>5</v>
-      </c>
-      <c r="F66" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="1:6">
+      <c r="D66" s="4">
+        <v>10</v>
+      </c>
+      <c r="E66" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F66" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G66" s="2">
+        <v>3</v>
+      </c>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A67" s="1">
         <v>10049</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>25</v>
+      <c r="B67" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C67" s="1">
         <v>0</v>
       </c>
-      <c r="D67" s="1">
-        <v>50</v>
-      </c>
-      <c r="E67" s="1">
-        <v>6</v>
-      </c>
-      <c r="F67" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" spans="1:6">
+      <c r="D67" s="4">
+        <v>10</v>
+      </c>
+      <c r="E67" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F67" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G67" s="2">
+        <v>3</v>
+      </c>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A68" s="1">
         <v>10050</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>25</v>
+      <c r="B68" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C68" s="1">
         <v>0</v>
       </c>
-      <c r="D68" s="1">
-        <v>50</v>
-      </c>
-      <c r="E68" s="1">
-        <v>7</v>
-      </c>
-      <c r="F68" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" spans="1:6">
+      <c r="D68" s="4">
+        <v>10</v>
+      </c>
+      <c r="E68" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F68" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G68" s="2">
+        <v>3</v>
+      </c>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A69" s="1">
         <v>10051</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>25</v>
+      <c r="B69" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C69" s="1">
         <v>0</v>
       </c>
-      <c r="D69" s="1">
-        <v>50</v>
-      </c>
-      <c r="E69" s="1">
-        <v>8</v>
-      </c>
-      <c r="F69" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" spans="1:6">
+      <c r="D69" s="4">
+        <v>10</v>
+      </c>
+      <c r="E69" s="4">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G69" s="2">
+        <v>3</v>
+      </c>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
+      <c r="O69" s="6"/>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A70" s="1">
         <v>10052</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>25</v>
+      <c r="B70" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C70" s="1">
         <v>0</v>
       </c>
-      <c r="D70" s="1">
-        <v>50</v>
-      </c>
-      <c r="E70" s="1">
-        <v>9</v>
-      </c>
-      <c r="F70" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" spans="1:6">
+      <c r="D70" s="4">
+        <v>10</v>
+      </c>
+      <c r="E70" s="4">
+        <v>1</v>
+      </c>
+      <c r="F70" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G70" s="2">
+        <v>3</v>
+      </c>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
+    </row>
+    <row r="71" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A71" s="1">
         <v>10053</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>25</v>
+      <c r="B71" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C71" s="1">
         <v>0</v>
       </c>
-      <c r="D71" s="1">
-        <v>50</v>
-      </c>
-      <c r="E71" s="1">
+      <c r="D71" s="4">
         <v>10</v>
       </c>
-      <c r="F71" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="72" s="1" customFormat="1" spans="1:6">
+      <c r="E71" s="4">
+        <v>2</v>
+      </c>
+      <c r="F71" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G71" s="2">
+        <v>3</v>
+      </c>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
+    </row>
+    <row r="72" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A72" s="1">
         <v>10054</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>30</v>
+      <c r="B72" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C72" s="1">
         <v>0</v>
       </c>
-      <c r="D72" s="1">
-        <v>51</v>
-      </c>
-      <c r="E72" s="1">
-        <v>5</v>
-      </c>
-      <c r="F72" s="1">
-        <v>20007</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" spans="1:6">
+      <c r="D72" s="4">
+        <v>10</v>
+      </c>
+      <c r="E72" s="4">
+        <v>3</v>
+      </c>
+      <c r="F72" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G72" s="2">
+        <v>3</v>
+      </c>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="6"/>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A73" s="1">
         <v>10055</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>23</v>
+      <c r="B73" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C73" s="1">
         <v>0</v>
       </c>
-      <c r="D73" s="1">
-        <v>52</v>
-      </c>
-      <c r="E73" s="1">
-        <v>7</v>
-      </c>
-      <c r="F73" s="1">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="74" s="1" customFormat="1" spans="1:6">
+      <c r="D73" s="4">
+        <v>10</v>
+      </c>
+      <c r="E73" s="4">
+        <v>4</v>
+      </c>
+      <c r="F73" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G73" s="2">
+        <v>3</v>
+      </c>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
+    </row>
+    <row r="74" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A74" s="1">
         <v>10056</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>24</v>
+      <c r="B74" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C74" s="1">
         <v>0</v>
       </c>
-      <c r="D74" s="1">
-        <v>53</v>
-      </c>
-      <c r="E74" s="1">
+      <c r="D74" s="4">
+        <v>10</v>
+      </c>
+      <c r="E74" s="4">
         <v>5</v>
       </c>
-      <c r="F74" s="1">
-        <v>20002</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" spans="1:6">
-      <c r="A75" s="1">
+      <c r="F74" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G74" s="2">
+        <v>3</v>
+      </c>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
+    </row>
+    <row r="75" s="2" customFormat="1" ht="14.25" spans="1:15">
+      <c r="A75" s="2">
         <v>10057</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C75" s="1">
-        <v>0</v>
-      </c>
-      <c r="D75" s="1">
-        <v>54</v>
-      </c>
-      <c r="E75" s="1">
-        <v>5</v>
-      </c>
-      <c r="F75" s="1">
-        <v>20003</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" spans="1:6">
+      <c r="B75" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="2">
+        <v>0</v>
+      </c>
+      <c r="D75" s="4">
+        <v>11</v>
+      </c>
+      <c r="E75" s="4">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4">
+        <v>20001</v>
+      </c>
+      <c r="G75" s="2">
+        <v>3</v>
+      </c>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6"/>
+    </row>
+    <row r="76" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A76" s="1">
         <v>10058</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>29</v>
+      <c r="B76" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C76" s="1">
         <v>0</v>
       </c>
-      <c r="D76" s="1">
-        <v>55</v>
-      </c>
-      <c r="E76" s="1">
+      <c r="D76" s="4">
+        <v>-6</v>
+      </c>
+      <c r="E76" s="4">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4">
+        <v>20002</v>
+      </c>
+      <c r="G76" s="1">
         <v>4</v>
       </c>
-      <c r="F76" s="1">
-        <v>20003</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="1:6">
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="6"/>
+    </row>
+    <row r="77" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A77" s="1">
         <v>10059</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>29</v>
+      <c r="B77" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C77" s="1">
         <v>0</v>
       </c>
-      <c r="D77" s="1">
-        <v>55</v>
-      </c>
-      <c r="E77" s="1">
-        <v>6</v>
-      </c>
-      <c r="F77" s="1">
+      <c r="D77" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E77" s="4">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4">
         <v>20003</v>
       </c>
-    </row>
-    <row r="78" s="1" customFormat="1" spans="1:6">
+      <c r="G77" s="1">
+        <v>4</v>
+      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="6"/>
+      <c r="O77" s="6"/>
+    </row>
+    <row r="78" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A78" s="1">
         <v>10060</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>23</v>
+      <c r="B78" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C78" s="1">
         <v>0</v>
       </c>
-      <c r="D78" s="1">
-        <v>56</v>
-      </c>
-      <c r="E78" s="1">
+      <c r="D78" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E78" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F78" s="4">
+        <v>20003</v>
+      </c>
+      <c r="G78" s="1">
         <v>4</v>
       </c>
-      <c r="F78" s="1">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="79" s="1" customFormat="1" spans="1:6">
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
+    </row>
+    <row r="79" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A79" s="1">
         <v>10061</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="1">
         <v>0</v>
       </c>
-      <c r="D79" s="1">
-        <v>56</v>
-      </c>
-      <c r="E79" s="1">
-        <v>5</v>
-      </c>
-      <c r="F79" s="1">
-        <v>10002</v>
-      </c>
-    </row>
-    <row r="80" s="1" customFormat="1" spans="1:6">
+      <c r="D79" s="4">
+        <v>-4</v>
+      </c>
+      <c r="E79" s="4">
+        <v>1</v>
+      </c>
+      <c r="F79" s="4">
+        <v>20003</v>
+      </c>
+      <c r="G79" s="1">
+        <v>4</v>
+      </c>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="6"/>
+    </row>
+    <row r="80" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A80" s="1">
         <v>10062</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>23</v>
+      <c r="B80" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C80" s="1">
         <v>0</v>
       </c>
-      <c r="D80" s="1">
-        <v>57</v>
-      </c>
-      <c r="E80" s="1">
-        <v>6</v>
-      </c>
-      <c r="F80" s="1">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" spans="1:6">
+      <c r="D80" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E80" s="4">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4">
+        <v>10002</v>
+      </c>
+      <c r="G80" s="1">
+        <v>4</v>
+      </c>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="6"/>
+    </row>
+    <row r="81" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A81" s="1">
         <v>10063</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C81" s="1">
         <v>0</v>
       </c>
-      <c r="D81" s="1">
-        <v>68</v>
-      </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" spans="1:6">
+      <c r="D81" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E81" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F81" s="4">
+        <v>10001</v>
+      </c>
+      <c r="G81" s="1">
+        <v>4</v>
+      </c>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="6"/>
+      <c r="O81" s="6"/>
+    </row>
+    <row r="82" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A82" s="1">
         <v>10064</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C82" s="1">
         <v>0</v>
       </c>
-      <c r="D82" s="1">
-        <v>68</v>
-      </c>
-      <c r="E82" s="1">
-        <v>2</v>
-      </c>
-      <c r="F82" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" spans="1:6">
+      <c r="D82" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="4">
+        <v>10001</v>
+      </c>
+      <c r="G82" s="1">
+        <v>4</v>
+      </c>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="6"/>
+      <c r="O82" s="6"/>
+    </row>
+    <row r="83" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A83" s="1">
         <v>10065</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>25</v>
+      <c r="B83" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C83" s="1">
         <v>0</v>
       </c>
-      <c r="D83" s="1">
-        <v>68</v>
-      </c>
-      <c r="E83" s="1">
-        <v>3</v>
-      </c>
-      <c r="F83" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" spans="1:6">
+      <c r="D83" s="4">
+        <v>9</v>
+      </c>
+      <c r="E83" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F83" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G83" s="1">
+        <v>4</v>
+      </c>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="6"/>
+      <c r="O83" s="6"/>
+    </row>
+    <row r="84" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A84" s="1">
         <v>10066</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>25</v>
+      <c r="B84" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C84" s="1">
         <v>0</v>
       </c>
-      <c r="D84" s="1">
-        <v>68</v>
-      </c>
-      <c r="E84" s="1">
+      <c r="D84" s="4">
+        <v>9</v>
+      </c>
+      <c r="E84" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F84" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G84" s="1">
         <v>4</v>
       </c>
-      <c r="F84" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" spans="1:6">
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="6"/>
+      <c r="O84" s="6"/>
+    </row>
+    <row r="85" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A85" s="1">
         <v>10067</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>25</v>
+      <c r="B85" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C85" s="1">
         <v>0</v>
       </c>
-      <c r="D85" s="1">
-        <v>68</v>
-      </c>
-      <c r="E85" s="1">
-        <v>5</v>
-      </c>
-      <c r="F85" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" spans="1:6">
+      <c r="D85" s="4">
+        <v>9</v>
+      </c>
+      <c r="E85" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F85" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G85" s="1">
+        <v>4</v>
+      </c>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="6"/>
+      <c r="O85" s="6"/>
+    </row>
+    <row r="86" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A86" s="1">
         <v>10068</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>25</v>
+      <c r="B86" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C86" s="1">
         <v>0</v>
       </c>
-      <c r="D86" s="1">
-        <v>68</v>
-      </c>
-      <c r="E86" s="1">
-        <v>6</v>
-      </c>
-      <c r="F86" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="87" s="1" customFormat="1" spans="1:6">
+      <c r="D86" s="4">
+        <v>9</v>
+      </c>
+      <c r="E86" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F86" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G86" s="1">
+        <v>4</v>
+      </c>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="6"/>
+    </row>
+    <row r="87" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A87" s="1">
         <v>10069</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>25</v>
+      <c r="B87" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
       </c>
-      <c r="D87" s="1">
-        <v>68</v>
-      </c>
-      <c r="E87" s="1">
-        <v>7</v>
-      </c>
-      <c r="F87" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" spans="1:6">
+      <c r="D87" s="4">
+        <v>9</v>
+      </c>
+      <c r="E87" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F87" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G87" s="1">
+        <v>4</v>
+      </c>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="6"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="6"/>
+    </row>
+    <row r="88" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A88" s="1">
         <v>10070</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>25</v>
+      <c r="B88" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C88" s="1">
         <v>0</v>
       </c>
-      <c r="D88" s="1">
-        <v>68</v>
-      </c>
-      <c r="E88" s="1">
-        <v>8</v>
-      </c>
-      <c r="F88" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" spans="1:6">
+      <c r="D88" s="4">
+        <v>9</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G88" s="1">
+        <v>4</v>
+      </c>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="6"/>
+    </row>
+    <row r="89" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A89" s="1">
         <v>10071</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>25</v>
+      <c r="B89" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C89" s="1">
         <v>0</v>
       </c>
-      <c r="D89" s="1">
-        <v>68</v>
-      </c>
-      <c r="E89" s="1">
+      <c r="D89" s="4">
         <v>9</v>
       </c>
-      <c r="F89" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" spans="1:6">
+      <c r="E89" s="4">
+        <v>1</v>
+      </c>
+      <c r="F89" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G89" s="1">
+        <v>4</v>
+      </c>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="6"/>
+      <c r="N89" s="6"/>
+      <c r="O89" s="6"/>
+    </row>
+    <row r="90" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A90" s="1">
         <v>10072</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>25</v>
+      <c r="B90" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C90" s="1">
         <v>0</v>
       </c>
-      <c r="D90" s="1">
-        <v>68</v>
-      </c>
-      <c r="E90" s="1">
-        <v>10</v>
-      </c>
-      <c r="F90" s="1">
-        <v>10006</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" spans="1:6">
+      <c r="D90" s="4">
+        <v>9</v>
+      </c>
+      <c r="E90" s="4">
+        <v>2</v>
+      </c>
+      <c r="F90" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G90" s="1">
+        <v>4</v>
+      </c>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="6"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="6"/>
+    </row>
+    <row r="91" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A91" s="1">
         <v>10073</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>26</v>
+      <c r="B91" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C91" s="1">
         <v>0</v>
       </c>
-      <c r="D91" s="1">
-        <v>69</v>
-      </c>
-      <c r="E91" s="1">
-        <v>5</v>
-      </c>
-      <c r="F91" s="1">
-        <v>20001</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" spans="1:6">
+      <c r="D91" s="4">
+        <v>9</v>
+      </c>
+      <c r="E91" s="4">
+        <v>3</v>
+      </c>
+      <c r="F91" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G91" s="1">
+        <v>4</v>
+      </c>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="6"/>
+    </row>
+    <row r="92" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A92" s="1">
         <v>10074</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>31</v>
+      <c r="B92" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C92" s="1">
         <v>0</v>
       </c>
-      <c r="D92" s="1">
-        <v>71</v>
-      </c>
-      <c r="E92" s="1">
-        <v>5</v>
-      </c>
-      <c r="F92" s="1">
-        <v>10002</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" spans="1:6">
+      <c r="D92" s="4">
+        <v>9</v>
+      </c>
+      <c r="E92" s="4">
+        <v>4</v>
+      </c>
+      <c r="F92" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G92" s="1">
+        <v>4</v>
+      </c>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="6"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="6"/>
+    </row>
+    <row r="93" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A93" s="1">
         <v>10075</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>24</v>
+      <c r="B93" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C93" s="1">
         <v>0</v>
       </c>
-      <c r="D93" s="1">
-        <v>74</v>
-      </c>
-      <c r="E93" s="1">
-        <v>3</v>
-      </c>
-      <c r="F93" s="1">
-        <v>20002</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" spans="1:6">
+      <c r="D93" s="4">
+        <v>9</v>
+      </c>
+      <c r="E93" s="4">
+        <v>5</v>
+      </c>
+      <c r="F93" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G93" s="1">
+        <v>4</v>
+      </c>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="6"/>
+    </row>
+    <row r="94" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A94" s="1">
         <v>10076</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>27</v>
+      <c r="B94" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C94" s="1">
         <v>2</v>
       </c>
-      <c r="D94" s="1">
-        <v>74</v>
-      </c>
-      <c r="E94" s="1">
-        <v>7</v>
-      </c>
-      <c r="F94" s="1">
-        <v>20004</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" spans="1:6">
+      <c r="D94" s="4">
+        <v>10</v>
+      </c>
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4">
+        <v>20001</v>
+      </c>
+      <c r="G94" s="1">
+        <v>4</v>
+      </c>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
+    </row>
+    <row r="95" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A95" s="1">
         <v>10077</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>28</v>
+      <c r="B95" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
       </c>
-      <c r="D95" s="1">
-        <v>81</v>
-      </c>
-      <c r="E95" s="1">
-        <v>3</v>
-      </c>
-      <c r="F95" s="1">
-        <v>10003</v>
-      </c>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="1:6">
+      <c r="D95" s="4">
+        <v>-6</v>
+      </c>
+      <c r="E95" s="4">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4">
+        <v>10002</v>
+      </c>
+      <c r="G95" s="1">
+        <v>5</v>
+      </c>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="6"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="6"/>
+    </row>
+    <row r="96" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A96" s="1">
         <v>10078</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>27</v>
+      <c r="B96" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
       </c>
-      <c r="D96" s="1">
-        <v>81</v>
-      </c>
-      <c r="E96" s="1">
-        <v>7</v>
-      </c>
-      <c r="F96" s="1">
+      <c r="D96" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E96" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F96" s="4">
+        <v>20002</v>
+      </c>
+      <c r="G96" s="1">
+        <v>5</v>
+      </c>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="6"/>
+      <c r="N96" s="6"/>
+      <c r="O96" s="6"/>
+    </row>
+    <row r="97" ht="14.25" spans="1:15">
+      <c r="A97" s="1">
+        <v>10079</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0</v>
+      </c>
+      <c r="D97" s="4">
+        <v>-3</v>
+      </c>
+      <c r="E97" s="4">
+        <v>2</v>
+      </c>
+      <c r="F97" s="4">
         <v>20004</v>
+      </c>
+      <c r="G97" s="1">
+        <v>5</v>
+      </c>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="6"/>
+    </row>
+    <row r="98" ht="14.25" spans="1:15">
+      <c r="A98" s="1">
+        <v>10080</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0</v>
+      </c>
+      <c r="D98" s="4">
+        <v>4</v>
+      </c>
+      <c r="E98" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F98" s="4">
+        <v>10003</v>
+      </c>
+      <c r="G98" s="1">
+        <v>5</v>
+      </c>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="6"/>
+    </row>
+    <row r="99" s="2" customFormat="1" ht="14.25" spans="1:15">
+      <c r="A99" s="2">
+        <v>10081</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" s="1">
+        <v>0</v>
+      </c>
+      <c r="D99" s="4">
+        <v>4</v>
+      </c>
+      <c r="E99" s="4">
+        <v>2</v>
+      </c>
+      <c r="F99" s="4">
+        <v>20004</v>
+      </c>
+      <c r="G99" s="1">
+        <v>5</v>
+      </c>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="7"/>
+      <c r="N99" s="7"/>
+      <c r="O99" s="7"/>
+    </row>
+    <row r="100" ht="14.25" spans="1:15">
+      <c r="A100" s="2">
+        <v>10082</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100" s="1">
+        <v>0</v>
+      </c>
+      <c r="D100" s="4">
+        <v>8</v>
+      </c>
+      <c r="E100" s="4">
+        <v>-5</v>
+      </c>
+      <c r="F100" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G100" s="1">
+        <v>5</v>
+      </c>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+    </row>
+    <row r="101" ht="14.25" spans="1:15">
+      <c r="A101" s="2">
+        <v>10083</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C101" s="1">
+        <v>0</v>
+      </c>
+      <c r="D101" s="4">
+        <v>8</v>
+      </c>
+      <c r="E101" s="4">
+        <v>-4</v>
+      </c>
+      <c r="F101" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G101" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" ht="14.25" spans="1:15">
+      <c r="A102" s="2">
+        <v>10084</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C102" s="1">
+        <v>0</v>
+      </c>
+      <c r="D102" s="4">
+        <v>8</v>
+      </c>
+      <c r="E102" s="4">
+        <v>-3</v>
+      </c>
+      <c r="F102" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G102" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" ht="14.25" spans="1:15">
+      <c r="A103" s="2">
+        <v>10085</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C103" s="1">
+        <v>0</v>
+      </c>
+      <c r="D103" s="4">
+        <v>8</v>
+      </c>
+      <c r="E103" s="4">
+        <v>-2</v>
+      </c>
+      <c r="F103" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G103" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" ht="14.25" spans="1:15">
+      <c r="A104" s="2">
+        <v>10086</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C104" s="1">
+        <v>0</v>
+      </c>
+      <c r="D104" s="4">
+        <v>8</v>
+      </c>
+      <c r="E104" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F104" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G104" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" ht="14.25" spans="1:15">
+      <c r="A105" s="2">
+        <v>10087</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0</v>
+      </c>
+      <c r="D105" s="4">
+        <v>8</v>
+      </c>
+      <c r="E105" s="4">
+        <v>0</v>
+      </c>
+      <c r="F105" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G105" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" ht="14.25" spans="1:15">
+      <c r="A106" s="2">
+        <v>10088</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C106" s="1">
+        <v>0</v>
+      </c>
+      <c r="D106" s="4">
+        <v>8</v>
+      </c>
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G106" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" ht="14.25" spans="1:15">
+      <c r="A107" s="2">
+        <v>10089</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C107" s="1">
+        <v>0</v>
+      </c>
+      <c r="D107" s="4">
+        <v>8</v>
+      </c>
+      <c r="E107" s="4">
+        <v>2</v>
+      </c>
+      <c r="F107" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G107" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" ht="14.25" spans="1:15">
+      <c r="A108" s="2">
+        <v>10090</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108" s="1">
+        <v>0</v>
+      </c>
+      <c r="D108" s="4">
+        <v>8</v>
+      </c>
+      <c r="E108" s="4">
+        <v>3</v>
+      </c>
+      <c r="F108" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G108" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" ht="14.25" spans="1:15">
+      <c r="A109" s="2">
+        <v>10091</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C109" s="1">
+        <v>0</v>
+      </c>
+      <c r="D109" s="4">
+        <v>8</v>
+      </c>
+      <c r="E109" s="4">
+        <v>4</v>
+      </c>
+      <c r="F109" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G109" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" ht="14.25" spans="1:15">
+      <c r="A110" s="2">
+        <v>10092</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110" s="1">
+        <v>0</v>
+      </c>
+      <c r="D110" s="4">
+        <v>8</v>
+      </c>
+      <c r="E110" s="4">
+        <v>5</v>
+      </c>
+      <c r="F110" s="4">
+        <v>10006</v>
+      </c>
+      <c r="G110" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" ht="14.25" spans="1:15">
+      <c r="A111" s="2">
+        <v>10093</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C111" s="1">
+        <v>0</v>
+      </c>
+      <c r="D111" s="4">
+        <v>9</v>
+      </c>
+      <c r="E111" s="4">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4">
+        <v>20001</v>
+      </c>
+      <c r="G111" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
